--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/56.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/56.xlsx
@@ -426,13 +426,13 @@
         <v>-8.662515355395263</v>
       </c>
       <c r="E2">
-        <v>-8.011221288775054</v>
+        <v>-12.35694419939187</v>
       </c>
       <c r="F2">
-        <v>-0.2448233047774988</v>
+        <v>-0.7172080998979449</v>
       </c>
       <c r="G2">
-        <v>-6.19754392512362</v>
+        <v>-9.424569548070988</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.399468291827038</v>
       </c>
       <c r="E3">
-        <v>-8.164211254650191</v>
+        <v>-12.63589819826436</v>
       </c>
       <c r="F3">
-        <v>0.05743802009520717</v>
+        <v>-0.450429064356753</v>
       </c>
       <c r="G3">
-        <v>-7.266841531801702</v>
+        <v>-9.246382811285342</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.056018042035458</v>
       </c>
       <c r="E4">
-        <v>-8.988882599239023</v>
+        <v>-13.39569915269332</v>
       </c>
       <c r="F4">
-        <v>-0.1170426626912583</v>
+        <v>-0.1389513237604996</v>
       </c>
       <c r="G4">
-        <v>-7.221006147837818</v>
+        <v>-9.833222724748911</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.668023283367657</v>
       </c>
       <c r="E5">
-        <v>-10.08178451625019</v>
+        <v>-13.53989935051956</v>
       </c>
       <c r="F5">
-        <v>0.2503921243315044</v>
+        <v>-0.7192458837088317</v>
       </c>
       <c r="G5">
-        <v>-6.677363516204339</v>
+        <v>-9.391120775494008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.248792582667758</v>
       </c>
       <c r="E6">
-        <v>-10.59772261689209</v>
+        <v>-13.59215341209407</v>
       </c>
       <c r="F6">
-        <v>0.2219782940480786</v>
+        <v>-0.2171508633195786</v>
       </c>
       <c r="G6">
-        <v>-6.778835292930167</v>
+        <v>-8.101745076380849</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.823699388934535</v>
       </c>
       <c r="E7">
-        <v>-11.09668799695324</v>
+        <v>-13.75909107791283</v>
       </c>
       <c r="F7">
-        <v>0.3223921622480319</v>
+        <v>0.5522003322348791</v>
       </c>
       <c r="G7">
-        <v>-7.308896948529104</v>
+        <v>-7.672285673794487</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.406861573538345</v>
       </c>
       <c r="E8">
-        <v>-11.84356015809029</v>
+        <v>-14.78017592563635</v>
       </c>
       <c r="F8">
-        <v>0.4954555084083074</v>
+        <v>0.1171102943232724</v>
       </c>
       <c r="G8">
-        <v>-5.840445301587692</v>
+        <v>-8.852557474834549</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.026651552875089</v>
       </c>
       <c r="E9">
-        <v>-13.16900827234335</v>
+        <v>-16.91089087335537</v>
       </c>
       <c r="F9">
-        <v>0.2068142003724308</v>
+        <v>-0.1046610551216141</v>
       </c>
       <c r="G9">
-        <v>-5.591436678662991</v>
+        <v>-6.877304751929103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.700171193407883</v>
       </c>
       <c r="E10">
-        <v>-13.0663749374335</v>
+        <v>-17.35029776326764</v>
       </c>
       <c r="F10">
-        <v>0.3929301316986181</v>
+        <v>0.639431561586681</v>
       </c>
       <c r="G10">
-        <v>-5.046219060680979</v>
+        <v>-8.342402990436764</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.441248500014689</v>
       </c>
       <c r="E11">
-        <v>-13.58536522955657</v>
+        <v>-16.84482496605747</v>
       </c>
       <c r="F11">
-        <v>0.315413166879446</v>
+        <v>0.8827007018690203</v>
       </c>
       <c r="G11">
-        <v>-4.355059270177985</v>
+        <v>-8.774425027061051</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.258128660326182</v>
       </c>
       <c r="E12">
-        <v>-15.0694367313503</v>
+        <v>-19.22333801147621</v>
       </c>
       <c r="F12">
-        <v>0.237288180386619</v>
+        <v>0.1251429730282192</v>
       </c>
       <c r="G12">
-        <v>-3.911057493640164</v>
+        <v>-7.539468387511285</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.148419541574051</v>
       </c>
       <c r="E13">
-        <v>-16.24117032388699</v>
+        <v>-19.45743747530273</v>
       </c>
       <c r="F13">
-        <v>0.8681313759885825</v>
+        <v>0.4891814536995039</v>
       </c>
       <c r="G13">
-        <v>-4.183169197564914</v>
+        <v>-5.801382358922503</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.118271036500277</v>
       </c>
       <c r="E14">
-        <v>-17.02388988526877</v>
+        <v>-21.28705418625174</v>
       </c>
       <c r="F14">
-        <v>0.6377110424910665</v>
+        <v>0.3052441286426792</v>
       </c>
       <c r="G14">
-        <v>-3.10224622290172</v>
+        <v>-5.247938718490962</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.16423466837262</v>
       </c>
       <c r="E15">
-        <v>-16.59679138770935</v>
+        <v>-22.08448223121043</v>
       </c>
       <c r="F15">
-        <v>1.031409218019588</v>
+        <v>0.6072370624768783</v>
       </c>
       <c r="G15">
-        <v>-3.320280114305262</v>
+        <v>-4.109554991878772</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.278954744395002</v>
       </c>
       <c r="E16">
-        <v>-18.53870066862656</v>
+        <v>-21.1808750561939</v>
       </c>
       <c r="F16">
-        <v>1.003325906329879</v>
+        <v>0.8366186232512838</v>
       </c>
       <c r="G16">
-        <v>-2.880032055231445</v>
+        <v>-5.523164301675625</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.453014352510367</v>
       </c>
       <c r="E17">
-        <v>-18.39155243422132</v>
+        <v>-23.16259868058655</v>
       </c>
       <c r="F17">
-        <v>0.7330528170836783</v>
+        <v>0.9278450685867877</v>
       </c>
       <c r="G17">
-        <v>-2.406929124682909</v>
+        <v>-4.752398794918943</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.669544348797618</v>
       </c>
       <c r="E18">
-        <v>-20.34668938771495</v>
+        <v>-22.51476877447125</v>
       </c>
       <c r="F18">
-        <v>1.410662322778091</v>
+        <v>1.856935320627491</v>
       </c>
       <c r="G18">
-        <v>-1.789144010692217</v>
+        <v>-4.779764182724712</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.923193532892117</v>
       </c>
       <c r="E19">
-        <v>-20.91820997832699</v>
+        <v>-22.20519323435889</v>
       </c>
       <c r="F19">
-        <v>1.329669528336772</v>
+        <v>1.023140454604843</v>
       </c>
       <c r="G19">
-        <v>-1.479209665851748</v>
+        <v>-5.270864613526802</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.206064119976086</v>
       </c>
       <c r="E20">
-        <v>-22.09178665978481</v>
+        <v>-24.60945971145926</v>
       </c>
       <c r="F20">
-        <v>1.537482058677084</v>
+        <v>1.630834094768171</v>
       </c>
       <c r="G20">
-        <v>-0.9057308865782381</v>
+        <v>-3.480433257400199</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.510786592130692</v>
       </c>
       <c r="E21">
-        <v>-20.86693859561215</v>
+        <v>-26.32421167920371</v>
       </c>
       <c r="F21">
-        <v>1.812034493926146</v>
+        <v>2.289227133452441</v>
       </c>
       <c r="G21">
-        <v>-1.724136449156499</v>
+        <v>-3.637177211294873</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.831853130713709</v>
       </c>
       <c r="E22">
-        <v>-22.78040453128719</v>
+        <v>-24.84651626881278</v>
       </c>
       <c r="F22">
-        <v>1.909619487445539</v>
+        <v>1.480498665038506</v>
       </c>
       <c r="G22">
-        <v>-0.5811885433551207</v>
+        <v>-3.000511948451136</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.159236893156806</v>
       </c>
       <c r="E23">
-        <v>-23.34368329920527</v>
+        <v>-26.3082035235866</v>
       </c>
       <c r="F23">
-        <v>1.502029590572071</v>
+        <v>2.278849346630169</v>
       </c>
       <c r="G23">
-        <v>-0.09989568379421038</v>
+        <v>-4.632617801891413</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.493661098811715</v>
       </c>
       <c r="E24">
-        <v>-23.40679211297617</v>
+        <v>-26.20094208824092</v>
       </c>
       <c r="F24">
-        <v>1.915086712304016</v>
+        <v>1.881290979004602</v>
       </c>
       <c r="G24">
-        <v>-0.887372451953145</v>
+        <v>-3.184929724978167</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.835276227048885</v>
       </c>
       <c r="E25">
-        <v>-23.68114518225687</v>
+        <v>-26.68866779581503</v>
       </c>
       <c r="F25">
-        <v>2.115697416444389</v>
+        <v>2.205664743327638</v>
       </c>
       <c r="G25">
-        <v>0.05937809192279557</v>
+        <v>-3.462711379757638</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.182653255695252</v>
       </c>
       <c r="E26">
-        <v>-23.8715629858054</v>
+        <v>-27.67212102453481</v>
       </c>
       <c r="F26">
-        <v>1.504209853576239</v>
+        <v>2.30613742561319</v>
       </c>
       <c r="G26">
-        <v>-0.524518565801951</v>
+        <v>-2.118125846685263</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.533879402939267</v>
       </c>
       <c r="E27">
-        <v>-23.12538820966552</v>
+        <v>-26.66932215485426</v>
       </c>
       <c r="F27">
-        <v>1.95048616489525</v>
+        <v>2.87626129058995</v>
       </c>
       <c r="G27">
-        <v>-0.200458562148072</v>
+        <v>-3.525989737531529</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.880110980155031</v>
       </c>
       <c r="E28">
-        <v>-23.65689520394579</v>
+        <v>-26.84091962042692</v>
       </c>
       <c r="F28">
-        <v>1.804976803654295</v>
+        <v>2.10142961629857</v>
       </c>
       <c r="G28">
-        <v>0.308809992428664</v>
+        <v>-2.351771790268643</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.220863685084465</v>
       </c>
       <c r="E29">
-        <v>-23.17943101847306</v>
+        <v>-27.11658594716984</v>
       </c>
       <c r="F29">
-        <v>1.935391654081438</v>
+        <v>2.39682708887168</v>
       </c>
       <c r="G29">
-        <v>0.2772282349190086</v>
+        <v>-2.716840500972462</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.555237531132494</v>
       </c>
       <c r="E30">
-        <v>-21.93449917207639</v>
+        <v>-26.50885567839246</v>
       </c>
       <c r="F30">
-        <v>1.921880981741778</v>
+        <v>2.381944640112984</v>
       </c>
       <c r="G30">
-        <v>-0.5084963609271825</v>
+        <v>-3.00515815817931</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.878916332994892</v>
       </c>
       <c r="E31">
-        <v>-23.26050881710639</v>
+        <v>-25.79327527264841</v>
       </c>
       <c r="F31">
-        <v>2.24312020381262</v>
+        <v>1.434181330078374</v>
       </c>
       <c r="G31">
-        <v>0.1412150388369062</v>
+        <v>-3.67229612564561</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.18629650085424</v>
       </c>
       <c r="E32">
-        <v>-22.64313742716669</v>
+        <v>-24.97096326301757</v>
       </c>
       <c r="F32">
-        <v>1.798445955050623</v>
+        <v>1.877445697520806</v>
       </c>
       <c r="G32">
-        <v>-0.3401992259217036</v>
+        <v>-2.431059228031065</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.46425601269212</v>
       </c>
       <c r="E33">
-        <v>-22.21469850130099</v>
+        <v>-24.82213043628148</v>
       </c>
       <c r="F33">
-        <v>1.938199819576928</v>
+        <v>2.299311678214122</v>
       </c>
       <c r="G33">
-        <v>-1.018601627001577</v>
+        <v>-2.482872997676257</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.70813299024592</v>
       </c>
       <c r="E34">
-        <v>-21.45770520075679</v>
+        <v>-24.72422935670965</v>
       </c>
       <c r="F34">
-        <v>1.666458863292967</v>
+        <v>1.732166622417829</v>
       </c>
       <c r="G34">
-        <v>-1.050311352152051</v>
+        <v>-3.854125018362239</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.91411966164571</v>
       </c>
       <c r="E35">
-        <v>-20.39802869753991</v>
+        <v>-25.20514876785024</v>
       </c>
       <c r="F35">
-        <v>1.795604654859021</v>
+        <v>2.279314889110542</v>
       </c>
       <c r="G35">
-        <v>-1.449698359146102</v>
+        <v>-4.778205602483975</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.07613927045301</v>
       </c>
       <c r="E36">
-        <v>-19.76822211797514</v>
+        <v>-25.03053533858848</v>
       </c>
       <c r="F36">
-        <v>1.54431608975018</v>
+        <v>1.753642875702809</v>
       </c>
       <c r="G36">
-        <v>-1.468243823400083</v>
+        <v>-5.669992404017657</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.18950769486251</v>
       </c>
       <c r="E37">
-        <v>-19.75359514693036</v>
+        <v>-23.67906661268735</v>
       </c>
       <c r="F37">
-        <v>1.993195131448787</v>
+        <v>2.251213353337972</v>
       </c>
       <c r="G37">
-        <v>-1.473565964769503</v>
+        <v>-3.462192946751246</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.24512520234133</v>
       </c>
       <c r="E38">
-        <v>-18.8858082013145</v>
+        <v>-23.09378398956599</v>
       </c>
       <c r="F38">
-        <v>1.969081356353293</v>
+        <v>1.893971627206657</v>
       </c>
       <c r="G38">
-        <v>-2.687791846506698</v>
+        <v>-5.575542441429041</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.24491168314259</v>
       </c>
       <c r="E39">
-        <v>-19.02845513255611</v>
+        <v>-21.9357445024285</v>
       </c>
       <c r="F39">
-        <v>2.284084628615862</v>
+        <v>2.822921056788884</v>
       </c>
       <c r="G39">
-        <v>-3.003281299447308</v>
+        <v>-6.112363413440435</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.19424806313626</v>
       </c>
       <c r="E40">
-        <v>-16.99406988392826</v>
+        <v>-22.09143343881221</v>
       </c>
       <c r="F40">
-        <v>2.219940827147485</v>
+        <v>2.482771863646934</v>
       </c>
       <c r="G40">
-        <v>-2.94559086198915</v>
+        <v>-6.080299316361541</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.09733736483108</v>
       </c>
       <c r="E41">
-        <v>-17.50032157866775</v>
+        <v>-21.98184889630059</v>
       </c>
       <c r="F41">
-        <v>2.403024933779426</v>
+        <v>2.785757181629687</v>
       </c>
       <c r="G41">
-        <v>-4.271932803191013</v>
+        <v>-5.560829443956491</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.96023617076693</v>
       </c>
       <c r="E42">
-        <v>-16.26905213835222</v>
+        <v>-21.46972377077315</v>
       </c>
       <c r="F42">
-        <v>2.187110970239734</v>
+        <v>1.978034351242751</v>
       </c>
       <c r="G42">
-        <v>-3.854482671512218</v>
+        <v>-5.916996200569537</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.78449605330828</v>
       </c>
       <c r="E43">
-        <v>-14.59542324307142</v>
+        <v>-19.95182456814212</v>
       </c>
       <c r="F43">
-        <v>2.553539290868096</v>
+        <v>2.319220660373005</v>
       </c>
       <c r="G43">
-        <v>-3.965991704988387</v>
+        <v>-6.614104845759805</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.58066614781801</v>
       </c>
       <c r="E44">
-        <v>-14.84669468033502</v>
+        <v>-21.91081072454227</v>
       </c>
       <c r="F44">
-        <v>2.549708919997551</v>
+        <v>2.385238228906515</v>
       </c>
       <c r="G44">
-        <v>-4.221283867199424</v>
+        <v>-6.289231099159183</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.3607247899297</v>
       </c>
       <c r="E45">
-        <v>-14.26835420786743</v>
+        <v>-20.05472055454441</v>
       </c>
       <c r="F45">
-        <v>2.907885044559224</v>
+        <v>2.086785737351881</v>
       </c>
       <c r="G45">
-        <v>-4.376200180685487</v>
+        <v>-7.258047858022389</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.13165523085085</v>
       </c>
       <c r="E46">
-        <v>-14.60995511616203</v>
+        <v>-15.97766294985466</v>
       </c>
       <c r="F46">
-        <v>3.184849685685238</v>
+        <v>2.810588322896005</v>
       </c>
       <c r="G46">
-        <v>-4.386962587400466</v>
+        <v>-7.317385468703388</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.898606027544428</v>
       </c>
       <c r="E47">
-        <v>-12.93889386564358</v>
+        <v>-18.06669329433307</v>
       </c>
       <c r="F47">
-        <v>2.670468319977663</v>
+        <v>2.056505595309948</v>
       </c>
       <c r="G47">
-        <v>-3.776241943427259</v>
+        <v>-6.588416162170912</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.659980364165454</v>
       </c>
       <c r="E48">
-        <v>-11.79381939959004</v>
+        <v>-16.21913476936567</v>
       </c>
       <c r="F48">
-        <v>2.904755472511447</v>
+        <v>2.731008723243862</v>
       </c>
       <c r="G48">
-        <v>-5.169747208729395</v>
+        <v>-5.933956834810306</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.420200082605799</v>
       </c>
       <c r="E49">
-        <v>-12.22972577909438</v>
+        <v>-15.35603026587374</v>
       </c>
       <c r="F49">
-        <v>2.581912531148784</v>
+        <v>1.975138378802563</v>
       </c>
       <c r="G49">
-        <v>-4.894898966024067</v>
+        <v>-7.072750714117428</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.184431265813124</v>
       </c>
       <c r="E50">
-        <v>-10.80727322312302</v>
+        <v>-16.20022839038365</v>
       </c>
       <c r="F50">
-        <v>2.729038865560005</v>
+        <v>2.418896453217064</v>
       </c>
       <c r="G50">
-        <v>-4.889255264941823</v>
+        <v>-6.9500002155786</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.952084331594785</v>
       </c>
       <c r="E51">
-        <v>-9.162508821167114</v>
+        <v>-15.19978432718709</v>
       </c>
       <c r="F51">
-        <v>2.717403617020283</v>
+        <v>2.43958741420419</v>
       </c>
       <c r="G51">
-        <v>-5.523272581987087</v>
+        <v>-8.341727058795517</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.721405144083235</v>
       </c>
       <c r="E52">
-        <v>-8.895297155396507</v>
+        <v>-14.65684746451146</v>
       </c>
       <c r="F52">
-        <v>2.993619414014167</v>
+        <v>2.462433787173401</v>
       </c>
       <c r="G52">
-        <v>-5.044758917087027</v>
+        <v>-6.587392421044365</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.485896092917985</v>
       </c>
       <c r="E53">
-        <v>-8.886072653842884</v>
+        <v>-12.13827777498349</v>
       </c>
       <c r="F53">
-        <v>2.866133670723323</v>
+        <v>2.321329683780533</v>
       </c>
       <c r="G53">
-        <v>-5.006677059668111</v>
+        <v>-7.411536840130094</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.245438925537208</v>
       </c>
       <c r="E54">
-        <v>-7.652036315908665</v>
+        <v>-12.03550405737941</v>
       </c>
       <c r="F54">
-        <v>2.71062094472616</v>
+        <v>2.858509377147956</v>
       </c>
       <c r="G54">
-        <v>-5.736089331111112</v>
+        <v>-7.53133752048698</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.003071492300627</v>
       </c>
       <c r="E55">
-        <v>-7.756711992595966</v>
+        <v>-11.59218909439852</v>
       </c>
       <c r="F55">
-        <v>2.595471248797807</v>
+        <v>2.545040241315373</v>
       </c>
       <c r="G55">
-        <v>-5.39679789697829</v>
+        <v>-7.074781790262723</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.757973531957404</v>
       </c>
       <c r="E56">
-        <v>-6.544697623761048</v>
+        <v>-12.65931493735802</v>
       </c>
       <c r="F56">
-        <v>2.774387010658861</v>
+        <v>2.022749623645868</v>
       </c>
       <c r="G56">
-        <v>-6.11386949413622</v>
+        <v>-8.316921023806115</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.510218178562786</v>
       </c>
       <c r="E57">
-        <v>-5.284056501031766</v>
+        <v>-11.41167959197877</v>
       </c>
       <c r="F57">
-        <v>2.666586590328144</v>
+        <v>2.274384446329079</v>
       </c>
       <c r="G57">
-        <v>-6.572311926757157</v>
+        <v>-8.330397000750756</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.257671911238623</v>
       </c>
       <c r="E58">
-        <v>-5.603766765973293</v>
+        <v>-10.26981581399668</v>
       </c>
       <c r="F58">
-        <v>2.292351735295801</v>
+        <v>2.545755950751392</v>
       </c>
       <c r="G58">
-        <v>-5.523961638514571</v>
+        <v>-7.993884761278783</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.003894603836306</v>
       </c>
       <c r="E59">
-        <v>-6.369096987165615</v>
+        <v>-11.46936782236249</v>
       </c>
       <c r="F59">
-        <v>2.562669556381752</v>
+        <v>2.212328130715757</v>
       </c>
       <c r="G59">
-        <v>-6.267351913800806</v>
+        <v>-7.297678452017363</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.756726659677995</v>
       </c>
       <c r="E60">
-        <v>-5.722417313448265</v>
+        <v>-10.02929497402728</v>
       </c>
       <c r="F60">
-        <v>2.037365338100862</v>
+        <v>1.941997055751361</v>
       </c>
       <c r="G60">
-        <v>-6.479046485151501</v>
+        <v>-7.306816654060416</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.519680954614071</v>
       </c>
       <c r="E61">
-        <v>-3.781187303632197</v>
+        <v>-8.119764282264907</v>
       </c>
       <c r="F61">
-        <v>1.974483968554352</v>
+        <v>1.963188350649778</v>
       </c>
       <c r="G61">
-        <v>-6.096639799727575</v>
+        <v>-8.272240629831156</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.295944765030133</v>
       </c>
       <c r="E62">
-        <v>-3.253266860766002</v>
+        <v>-9.273633044841336</v>
       </c>
       <c r="F62">
-        <v>2.130869793794065</v>
+        <v>2.122241518926505</v>
       </c>
       <c r="G62">
-        <v>-5.722491948968773</v>
+        <v>-7.60526344222127</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.085219732806761</v>
       </c>
       <c r="E63">
-        <v>-4.250088144756424</v>
+        <v>-7.881951469752097</v>
       </c>
       <c r="F63">
-        <v>2.518118300724389</v>
+        <v>2.402960321122007</v>
       </c>
       <c r="G63">
-        <v>-5.97724927206562</v>
+        <v>-8.745619182990687</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.889317218968354</v>
       </c>
       <c r="E64">
-        <v>-3.037344691606272</v>
+        <v>-8.091176025854482</v>
       </c>
       <c r="F64">
-        <v>2.044510835317411</v>
+        <v>2.209201872137592</v>
       </c>
       <c r="G64">
-        <v>-5.352927964728515</v>
+        <v>-7.951648877365611</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.713222711071502</v>
       </c>
       <c r="E65">
-        <v>-2.678051035363698</v>
+        <v>-9.751975754271555</v>
       </c>
       <c r="F65">
-        <v>2.183582125103809</v>
+        <v>2.178436306797618</v>
       </c>
       <c r="G65">
-        <v>-6.330984643503117</v>
+        <v>-7.45930814481405</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.556621167787139</v>
       </c>
       <c r="E66">
-        <v>-2.043697867895227</v>
+        <v>-7.222732451507508</v>
       </c>
       <c r="F66">
-        <v>2.080669072449609</v>
+        <v>1.899766885556642</v>
       </c>
       <c r="G66">
-        <v>-5.209079211562458</v>
+        <v>-7.603028930339288</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.418199468283327</v>
       </c>
       <c r="E67">
-        <v>-2.463165886751724</v>
+        <v>-9.165026652715378</v>
       </c>
       <c r="F67">
-        <v>1.98191939436188</v>
+        <v>1.797809768885273</v>
       </c>
       <c r="G67">
-        <v>-5.755537131293941</v>
+        <v>-7.927951895263301</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.29379514065976</v>
       </c>
       <c r="E68">
-        <v>-2.600908480643033</v>
+        <v>-8.871404926532039</v>
       </c>
       <c r="F68">
-        <v>1.767607493379203</v>
+        <v>1.918758036633224</v>
       </c>
       <c r="G68">
-        <v>-5.193335910520243</v>
+        <v>-6.765306816440576</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.180551632517072</v>
       </c>
       <c r="E69">
-        <v>-2.612813838809199</v>
+        <v>-7.490546404321132</v>
       </c>
       <c r="F69">
-        <v>1.827707205187113</v>
+        <v>1.620391695288481</v>
       </c>
       <c r="G69">
-        <v>-4.748645077454938</v>
+        <v>-7.61843754678244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.080445467178401</v>
       </c>
       <c r="E70">
-        <v>-3.059208164115304</v>
+        <v>-7.733444693144556</v>
       </c>
       <c r="F70">
-        <v>1.750022910152575</v>
+        <v>1.833270520664315</v>
       </c>
       <c r="G70">
-        <v>-4.457794317204199</v>
+        <v>-6.351702276429451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.991807206243267</v>
       </c>
       <c r="E71">
-        <v>-2.758282009357594</v>
+        <v>-8.082168891053227</v>
       </c>
       <c r="F71">
-        <v>1.411543705694669</v>
+        <v>2.055304462575888</v>
       </c>
       <c r="G71">
-        <v>-3.638040172565007</v>
+        <v>-7.200560856300918</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.913513375924119</v>
       </c>
       <c r="E72">
-        <v>-2.261200474483634</v>
+        <v>-7.004994364270702</v>
       </c>
       <c r="F72">
-        <v>1.456456129539653</v>
+        <v>1.834022678266056</v>
       </c>
       <c r="G72">
-        <v>-4.140992375639811</v>
+        <v>-7.834538798687469</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.843374538652797</v>
       </c>
       <c r="E73">
-        <v>-3.563154865584892</v>
+        <v>-7.613154838078808</v>
       </c>
       <c r="F73">
-        <v>1.790574807989222</v>
+        <v>1.751444388615779</v>
       </c>
       <c r="G73">
-        <v>-3.304878060305228</v>
+        <v>-6.608096929084462</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.78016994396866</v>
       </c>
       <c r="E74">
-        <v>-2.128298819306524</v>
+        <v>-7.412602309701111</v>
       </c>
       <c r="F74">
-        <v>1.478394611835395</v>
+        <v>1.616925806075168</v>
       </c>
       <c r="G74">
-        <v>-3.202782851483106</v>
+        <v>-6.65543839374413</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.729189458049016</v>
       </c>
       <c r="E75">
-        <v>-2.729154864540258</v>
+        <v>-8.354384520602308</v>
       </c>
       <c r="F75">
-        <v>1.246216482709138</v>
+        <v>0.9924908607012611</v>
       </c>
       <c r="G75">
-        <v>-3.000344606151605</v>
+        <v>-6.922857950838874</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.692558325227107</v>
       </c>
       <c r="E76">
-        <v>-2.661467763547609</v>
+        <v>-7.853879459378549</v>
       </c>
       <c r="F76">
-        <v>0.8729458473336532</v>
+        <v>1.750924173886821</v>
       </c>
       <c r="G76">
-        <v>-3.081544996083183</v>
+        <v>-6.627797383327367</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.672896763613254</v>
       </c>
       <c r="E77">
-        <v>-4.019960152634632</v>
+        <v>-8.962264229021937</v>
       </c>
       <c r="F77">
-        <v>0.7827631449256767</v>
+        <v>1.095236583140095</v>
       </c>
       <c r="G77">
-        <v>-3.153790932379037</v>
+        <v>-6.077566058802524</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.671704926201373</v>
       </c>
       <c r="E78">
-        <v>-4.080628118915392</v>
+        <v>-9.21235373456954</v>
       </c>
       <c r="F78">
-        <v>1.219301169057377</v>
+        <v>1.231556036414393</v>
       </c>
       <c r="G78">
-        <v>-3.319486058687876</v>
+        <v>-5.486539306629104</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.688887620199405</v>
       </c>
       <c r="E79">
-        <v>-4.823338612439399</v>
+        <v>-9.992410553234805</v>
       </c>
       <c r="F79">
-        <v>0.7219560073557761</v>
+        <v>1.522579729100721</v>
       </c>
       <c r="G79">
-        <v>-1.080400153852159</v>
+        <v>-6.401776998648137</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.731241172002</v>
       </c>
       <c r="E80">
-        <v>-4.964821725861045</v>
+        <v>-10.44639912945178</v>
       </c>
       <c r="F80">
-        <v>0.9515579138593263</v>
+        <v>0.795016355547887</v>
       </c>
       <c r="G80">
-        <v>-1.600778924629174</v>
+        <v>-4.481648797941362</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.801081116814437</v>
       </c>
       <c r="E81">
-        <v>-5.590883257421472</v>
+        <v>-10.42603458183928</v>
       </c>
       <c r="F81">
-        <v>0.5866910657852421</v>
+        <v>1.753366200990274</v>
       </c>
       <c r="G81">
-        <v>-0.3681486711650537</v>
+        <v>-4.866496712205514</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.899956961934509</v>
       </c>
       <c r="E82">
-        <v>-6.447000325519568</v>
+        <v>-10.95839292923299</v>
       </c>
       <c r="F82">
-        <v>0.2864310765576997</v>
+        <v>1.128485593953662</v>
       </c>
       <c r="G82">
-        <v>-1.102837146875642</v>
+        <v>-3.749503268939344</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.027757444105206</v>
       </c>
       <c r="E83">
-        <v>-6.768793688504624</v>
+        <v>-12.26811818173141</v>
       </c>
       <c r="F83">
-        <v>0.7883165199940446</v>
+        <v>0.9509035036111148</v>
       </c>
       <c r="G83">
-        <v>-0.186542901514467</v>
+        <v>-6.217352659677987</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.180307192344382</v>
       </c>
       <c r="E84">
-        <v>-8.880719997565818</v>
+        <v>-14.49540736613801</v>
       </c>
       <c r="F84">
-        <v>0.6289038402645021</v>
+        <v>0.8466816304604922</v>
       </c>
       <c r="G84">
-        <v>0.2591519853480276</v>
+        <v>-4.493861504585615</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.362702762801328</v>
       </c>
       <c r="E85">
-        <v>-9.320964655169506</v>
+        <v>-12.26939973987558</v>
       </c>
       <c r="F85">
-        <v>0.4293393641538648</v>
+        <v>1.179632310872114</v>
       </c>
       <c r="G85">
-        <v>0.4797452295679364</v>
+        <v>-3.457881421622135</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.575047591844422</v>
       </c>
       <c r="E86">
-        <v>-10.01518877749339</v>
+        <v>-14.84591125433169</v>
       </c>
       <c r="F86">
-        <v>0.03471093203199993</v>
+        <v>-0.04226013866872733</v>
       </c>
       <c r="G86">
-        <v>0.1135609035339062</v>
+        <v>-3.738583363589512</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.817510097031927</v>
       </c>
       <c r="E87">
-        <v>-11.06978433287367</v>
+        <v>-16.68852921415673</v>
       </c>
       <c r="F87">
-        <v>0.09985540132295866</v>
+        <v>1.075387243434213</v>
       </c>
       <c r="G87">
-        <v>0.1556885071356169</v>
+        <v>-3.241058300974029</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.089075644042191</v>
       </c>
       <c r="E88">
-        <v>-12.57677897009422</v>
+        <v>-16.68743332344688</v>
       </c>
       <c r="F88">
-        <v>0.1796379509887874</v>
+        <v>0.6768762532954271</v>
       </c>
       <c r="G88">
-        <v>0.9275597855578324</v>
+        <v>-4.591153005044711</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.382975127684504</v>
       </c>
       <c r="E89">
-        <v>-14.86924648089322</v>
+        <v>-18.88967551811705</v>
       </c>
       <c r="F89">
-        <v>-0.2756634231837244</v>
+        <v>0.08012617489048282</v>
       </c>
       <c r="G89">
-        <v>0.05576218576428749</v>
+        <v>-3.246649502511322</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.705202470997589</v>
       </c>
       <c r="E90">
-        <v>-15.43812697115879</v>
+        <v>-21.58490097868424</v>
       </c>
       <c r="F90">
-        <v>-1.017022427462781</v>
+        <v>-0.1568970751747481</v>
       </c>
       <c r="G90">
-        <v>0.3817777974675955</v>
+        <v>-3.913981062049629</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.055990071924752</v>
       </c>
       <c r="E91">
-        <v>-16.51057829955132</v>
+        <v>-21.463732599661</v>
       </c>
       <c r="F91">
-        <v>-0.5982586826929499</v>
+        <v>-0.1115969753852543</v>
       </c>
       <c r="G91">
-        <v>1.23390119279071</v>
+        <v>-2.440407428253923</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.434818512557057</v>
       </c>
       <c r="E92">
-        <v>-20.20474436994452</v>
+        <v>-22.60600846877779</v>
       </c>
       <c r="F92">
-        <v>-0.8312800898352565</v>
+        <v>-0.3391826356303905</v>
       </c>
       <c r="G92">
-        <v>0.4880696886642477</v>
+        <v>-3.427369342340859</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.839392566433991</v>
       </c>
       <c r="E93">
-        <v>-21.44591305444082</v>
+        <v>-22.94727426999583</v>
       </c>
       <c r="F93">
-        <v>-1.19456972637441</v>
+        <v>-0.1489455764752756</v>
       </c>
       <c r="G93">
-        <v>1.340750891652468</v>
+        <v>-4.512689153893709</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.258203521452907</v>
       </c>
       <c r="E94">
-        <v>-22.67657567923932</v>
+        <v>-27.58213118905438</v>
       </c>
       <c r="F94">
-        <v>-1.467639383972462</v>
+        <v>-1.027077979365364</v>
       </c>
       <c r="G94">
-        <v>0.4745805868333705</v>
+        <v>-4.472569657886378</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.693082229405448</v>
       </c>
       <c r="E95">
-        <v>-25.0859910312864</v>
+        <v>-28.54273373793146</v>
       </c>
       <c r="F95">
-        <v>-1.560715573718417</v>
+        <v>-0.5482542844229578</v>
       </c>
       <c r="G95">
-        <v>0.4329025105853037</v>
+        <v>-3.4722695781603</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.138233928195278</v>
       </c>
       <c r="E96">
-        <v>-27.18436814611665</v>
+        <v>-29.935773855223</v>
       </c>
       <c r="F96">
-        <v>-1.858861569334015</v>
+        <v>-0.8617416443384026</v>
       </c>
       <c r="G96">
-        <v>0.2377256085648536</v>
+        <v>-4.384357297482267</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.583697517538958</v>
       </c>
       <c r="E97">
-        <v>-28.62320472104776</v>
+        <v>-33.61370761053571</v>
       </c>
       <c r="F97">
-        <v>-1.922715442211412</v>
+        <v>-1.301391016435018</v>
       </c>
       <c r="G97">
-        <v>-0.433654978377808</v>
+        <v>-4.990540012038762</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.01930852239305</v>
       </c>
       <c r="E98">
-        <v>-31.74686231476963</v>
+        <v>-35.0055952311923</v>
       </c>
       <c r="F98">
-        <v>-2.043280175851866</v>
+        <v>-1.053947732809972</v>
       </c>
       <c r="G98">
-        <v>-0.1318580630047614</v>
+        <v>-5.041576132174365</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.42019069588169</v>
       </c>
       <c r="E99">
-        <v>-34.51096812923049</v>
+        <v>-37.01106843751818</v>
       </c>
       <c r="F99">
-        <v>-2.197240541336182</v>
+        <v>-1.109933772095579</v>
       </c>
       <c r="G99">
-        <v>-0.6321098207361433</v>
+        <v>-5.0457400023333</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.78290352185803</v>
       </c>
       <c r="E100">
-        <v>-36.20488005959165</v>
+        <v>-39.49324051720949</v>
       </c>
       <c r="F100">
-        <v>-2.519124233246403</v>
+        <v>-1.383616421571702</v>
       </c>
       <c r="G100">
-        <v>-1.756279295552819</v>
+        <v>-5.308132727998975</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.08465310202059</v>
       </c>
       <c r="E101">
-        <v>-38.39646222644777</v>
+        <v>-40.97341073864562</v>
       </c>
       <c r="F101">
-        <v>-2.838401881307417</v>
+        <v>-1.496609048783166</v>
       </c>
       <c r="G101">
-        <v>-0.9902026544045829</v>
+        <v>-5.778508963431613</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.32161035463863</v>
       </c>
       <c r="E102">
-        <v>-39.3031397068415</v>
+        <v>-44.29546530711753</v>
       </c>
       <c r="F102">
-        <v>-2.742271500947339</v>
+        <v>-2.011357381250182</v>
       </c>
       <c r="G102">
-        <v>-2.210082080888701</v>
+        <v>-4.546643234590843</v>
       </c>
     </row>
   </sheetData>
